--- a/Excel Class Files/Part 3 Basic Operations.xlsx
+++ b/Excel Class Files/Part 3 Basic Operations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Desktop\Excel\Class file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Excel Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CA0782-36A9-485E-9302-209A39F2C5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18079F9C-E910-40DB-8EF8-DA62EC915201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
   <si>
     <t>Data</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Rectangle with length 10 cm and breadth 20 cm.</t>
   </si>
   <si>
-    <t>Triangle with sides 300 cm, 400cm, 5 m.</t>
-  </si>
-  <si>
     <t>Sphere with radius equal to 7 cm.</t>
   </si>
   <si>
@@ -186,9 +183,6 @@
   </si>
   <si>
     <t>Q5. Calculate Area of following shapes:</t>
-  </si>
-  <si>
-    <t>Hint -&gt;</t>
   </si>
   <si>
     <t>Q6. Calculate Volume of following figures:</t>
@@ -325,14 +319,17 @@
     <t>Product</t>
   </si>
   <si>
-    <t>Q4. Calculate Tax Amount (Tax 18%)</t>
+    <t>Q4. Calculate Tax Amount</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,6 +407,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -437,7 +441,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -517,11 +521,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -559,9 +573,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -572,9 +583,16 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -723,7 +741,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="228600" y="142875"/>
-          <a:ext cx="8965223" cy="1513010"/>
+          <a:ext cx="8984322" cy="1530134"/>
           <a:chOff x="228600" y="142875"/>
           <a:chExt cx="8818685" cy="1733550"/>
         </a:xfrm>
@@ -840,165 +858,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>36635</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>505557</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>102577</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="Straight Arrow Connector 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2469173" y="3766038"/>
-          <a:ext cx="3509596" cy="7327"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>36635</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>505557</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>102577</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2469173" y="3766038"/>
-          <a:ext cx="3509596" cy="7327"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>36635</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>505557</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>102577</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2469173" y="7436827"/>
-          <a:ext cx="3509596" cy="7327"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>556846</xdr:colOff>
       <xdr:row>8</xdr:row>
@@ -1023,8 +882,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1164981" y="1575289"/>
-          <a:ext cx="5370635" cy="1992924"/>
+          <a:off x="1166874" y="1592413"/>
+          <a:ext cx="5380267" cy="2014328"/>
           <a:chOff x="240323" y="1427283"/>
           <a:chExt cx="5882368" cy="2148255"/>
         </a:xfrm>
@@ -1356,72 +1215,6 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>14653</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>91037</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>80595</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>58616</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5956788" y="8802749"/>
-          <a:ext cx="1890346" cy="927405"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF">
-            <a:shade val="85000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="88900" cap="sq">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="55000" dist="18000" dir="5400000" algn="tl" rotWithShape="0">
-            <a:srgbClr val="000000">
-              <a:alpha val="40000"/>
-            </a:srgbClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>80596</xdr:colOff>
       <xdr:row>73</xdr:row>
@@ -1447,7 +1240,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1497,7 +1290,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1788,45 +1581,45 @@
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" s="31" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:1" s="28" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:1" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+    <row r="3" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+    </row>
+    <row r="5" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="30" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:1" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+    <row r="7" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="30" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:1" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-    </row>
-    <row r="5" spans="1:1" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+    <row r="8" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:1" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:1" s="28" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="4:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D20" s="1"/>
     </row>
@@ -1847,8 +1640,8 @@
     <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="20" spans="1:14" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="27" t="s">
+    <row r="20" spans="1:14" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="31" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1988,8 +1781,8 @@
       </c>
       <c r="F36" s="5"/>
     </row>
-    <row r="39" spans="1:11" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="27" t="s">
+    <row r="39" spans="1:11" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="31" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2137,8 +1930,8 @@
       </c>
       <c r="C57" s="5"/>
     </row>
-    <row r="62" spans="1:6" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A62" s="27" t="s">
+    <row r="62" spans="1:6" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A62" s="31" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2594,7 +2387,7 @@
     </row>
     <row r="22" spans="1:7" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -2652,7 +2445,7 @@
     </row>
     <row r="35" spans="1:11" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="18"/>
@@ -2667,19 +2460,25 @@
     <row r="36" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>5</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>29</v>
+      </c>
+      <c r="H37" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I37" s="35">
+        <v>0.18</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2723,89 +2522,78 @@
     </row>
     <row r="45" spans="1:11" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
       <c r="F47" s="22"/>
-      <c r="H47" s="23" t="s">
-        <v>50</v>
-      </c>
+      <c r="H47" s="23"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
       <c r="F48" s="22"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="22"/>
     </row>
     <row r="54" spans="1:7" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B56" s="28" t="s">
+      <c r="B56" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="5"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="5"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="28" t="s">
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="5"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="C57" s="28"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="5"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B58" s="28" t="s">
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="5"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="5"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B59" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="29"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="33"/>
       <c r="G59" s="5"/>
     </row>
     <row r="62" spans="1:7" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -2841,72 +2629,72 @@
     </row>
     <row r="71" spans="1:8" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B73" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C73" s="28"/>
-      <c r="D73" s="28"/>
-      <c r="E73" s="29"/>
+      <c r="B73" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="33"/>
       <c r="F73" s="3">
         <v>12000</v>
       </c>
       <c r="H73" s="25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B74" s="28" t="s">
+      <c r="B74" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="33"/>
+      <c r="F74" s="36">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B75" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C74" s="28"/>
-      <c r="D74" s="28"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="3">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B75" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C75" s="28"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="29"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="33"/>
       <c r="F75" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B76" s="28" t="s">
+      <c r="B76" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="5"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B77" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C76" s="28"/>
-      <c r="D76" s="28"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="5"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B77" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C77" s="28"/>
-      <c r="D77" s="28"/>
-      <c r="E77" s="29"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="33"/>
       <c r="F77" s="5"/>
     </row>
     <row r="80" spans="1:8" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="G81" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
@@ -2914,14 +2702,14 @@
         <v>5</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E82" s="5"/>
       <c r="G82" s="25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
@@ -2929,14 +2717,14 @@
         <v>22</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E83" s="5"/>
       <c r="G83" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.25">
@@ -2944,10 +2732,10 @@
         <v>23</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E84" s="5"/>
     </row>
@@ -2956,18 +2744,17 @@
         <v>56</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E85" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="B47:E47"/>
     <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
     <mergeCell ref="B76:E76"/>
     <mergeCell ref="B77:E77"/>
     <mergeCell ref="B56:F56"/>

--- a/Excel Class Files/Part 3 Basic Operations.xlsx
+++ b/Excel Class Files/Part 3 Basic Operations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Excel Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18079F9C-E910-40DB-8EF8-DA62EC915201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F9672B-6C88-47BA-ACC3-2C870F58108D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Operators" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
-  <si>
-    <t>Data</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
   <si>
     <t>Try to insert this 8 using  ' = ' operator and cell reference and move it around with fill handle.</t>
   </si>
@@ -583,12 +580,12 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1583,17 +1580,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="28" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
@@ -1601,22 +1598,22 @@
     </row>
     <row r="5" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="28" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="28" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -1640,94 +1637,89 @@
     <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="20" spans="1:14" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="31" t="s">
-        <v>9</v>
+    <row r="20" spans="1:14" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="34" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N22" s="8"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B24">
         <v>1</v>
       </c>
-      <c r="N22" s="8"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="3">
-        <v>1</v>
-      </c>
-      <c r="C24" s="3">
+      <c r="C24">
         <v>2</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24">
         <v>4</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="3">
+      <c r="B25">
         <v>6</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25">
         <v>7</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25">
         <v>8</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25">
         <v>9</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25">
         <v>10</v>
       </c>
       <c r="K25" s="5"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="3">
+      <c r="B26">
         <v>11</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26">
         <v>12</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26">
         <v>13</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26">
         <v>14</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="3">
+      <c r="B27">
         <v>16</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27">
         <v>17</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27">
         <v>18</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27">
         <v>19</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27">
         <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D30" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
@@ -1736,13 +1728,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D32" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="F32" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1781,93 +1773,88 @@
       </c>
       <c r="F36" s="5"/>
     </row>
-    <row r="39" spans="1:11" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="31" t="s">
-        <v>8</v>
+    <row r="39" spans="1:11" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B44">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="3">
-        <v>1</v>
-      </c>
-      <c r="C43" s="3">
-        <v>2</v>
-      </c>
-      <c r="D43" s="3">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="3">
-        <v>6</v>
-      </c>
-      <c r="C44" s="3">
+      <c r="C44">
         <v>7</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44">
         <v>8</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44">
         <v>9</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44">
         <v>10</v>
       </c>
       <c r="K44" s="5"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B45" s="3">
+      <c r="B45">
         <v>11</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45">
         <v>12</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45">
         <v>13</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45">
         <v>14</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45">
         <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B46" s="3">
+      <c r="B46">
         <v>16</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46">
         <v>17</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46">
         <v>18</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46">
         <v>19</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46">
         <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -1876,10 +1863,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1888,7 +1875,7 @@
       </c>
       <c r="C51" s="5"/>
       <c r="E51" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F51" s="10">
         <v>0.18</v>
@@ -1930,93 +1917,88 @@
       </c>
       <c r="C57" s="5"/>
     </row>
-    <row r="62" spans="1:6" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A62" s="31" t="s">
-        <v>10</v>
+    <row r="62" spans="1:6" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A62" s="34" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66">
+        <v>3</v>
+      </c>
+      <c r="E66">
+        <v>4</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67">
         <v>7</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B65" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B66" s="3">
-        <v>1</v>
-      </c>
-      <c r="C66" s="3">
-        <v>2</v>
-      </c>
-      <c r="D66" s="3">
-        <v>3</v>
-      </c>
-      <c r="E66" s="3">
-        <v>4</v>
-      </c>
-      <c r="F66" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B67" s="3">
-        <v>6</v>
-      </c>
-      <c r="C67" s="3">
-        <v>7</v>
-      </c>
-      <c r="D67" s="4">
+      <c r="D67">
         <v>8</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E67">
         <v>9</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67">
         <v>10</v>
       </c>
       <c r="K67" s="5"/>
     </row>
     <row r="68" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B68" s="3">
+      <c r="B68">
         <v>11</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68">
         <v>12</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68">
         <v>13</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68">
         <v>14</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68">
         <v>15</v>
       </c>
     </row>
     <row r="69" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B69" s="3">
+      <c r="B69">
         <v>16</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69">
         <v>17</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69">
         <v>18</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E69">
         <v>19</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69">
         <v>20</v>
       </c>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C72" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -2024,17 +2006,17 @@
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J73" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K73" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L73" s="11"/>
       <c r="M73" s="12"/>
     </row>
     <row r="74" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C74" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D74" s="4">
         <v>1</v>
@@ -2052,7 +2034,7 @@
         <v>5</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K74" s="4">
         <v>1</v>
@@ -2263,16 +2245,16 @@
   <sheetData>
     <row r="2" spans="1:5" s="13" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2307,22 +2289,22 @@
     </row>
     <row r="12" spans="1:5" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="D14" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="E14" s="15" t="s">
         <v>25</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2387,16 +2369,16 @@
     </row>
     <row r="22" spans="1:7" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" s="26"/>
       <c r="G24" s="25"/>
@@ -2445,7 +2427,7 @@
     </row>
     <row r="35" spans="1:11" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="18"/>
@@ -2460,30 +2442,30 @@
     <row r="36" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C37" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H37" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="I37" s="35">
+      <c r="H37" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I37" s="32">
         <v>0.18</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38" s="5">
         <v>10</v>
@@ -2496,7 +2478,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C39" s="5">
         <v>12</v>
@@ -2509,7 +2491,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C40" s="5">
         <v>30</v>
@@ -2522,78 +2504,78 @@
     </row>
     <row r="45" spans="1:11" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
+      <c r="B47" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
       <c r="F47" s="22"/>
       <c r="H47" s="23"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
+      <c r="B48" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
       <c r="F48" s="22"/>
     </row>
     <row r="54" spans="1:7" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B56" s="32" t="s">
+      <c r="B56" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="5"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="33"/>
-      <c r="G56" s="5"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="32" t="s">
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="5"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="33"/>
-      <c r="G57" s="5"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B58" s="32" t="s">
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="5"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="5"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B59" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="33"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="36"/>
       <c r="G59" s="5"/>
     </row>
     <row r="62" spans="1:7" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -2629,72 +2611,72 @@
     </row>
     <row r="71" spans="1:8" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B73" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="33"/>
+      <c r="B73" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C73" s="35"/>
+      <c r="D73" s="35"/>
+      <c r="E73" s="36"/>
       <c r="F73" s="3">
         <v>12000</v>
       </c>
       <c r="H73" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B74" s="32" t="s">
+      <c r="B74" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C74" s="35"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="33">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B75" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="33"/>
-      <c r="F74" s="36">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B75" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
-      <c r="E75" s="33"/>
+      <c r="C75" s="35"/>
+      <c r="D75" s="35"/>
+      <c r="E75" s="36"/>
       <c r="F75" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B76" s="32" t="s">
+      <c r="B76" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="5"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B77" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="33"/>
-      <c r="F76" s="5"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B77" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C77" s="32"/>
-      <c r="D77" s="32"/>
-      <c r="E77" s="33"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="35"/>
+      <c r="E77" s="36"/>
       <c r="F77" s="5"/>
     </row>
     <row r="80" spans="1:8" s="14" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="G81" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
@@ -2702,14 +2684,14 @@
         <v>5</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E82" s="5"/>
       <c r="G82" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
@@ -2717,14 +2699,14 @@
         <v>22</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E83" s="5"/>
       <c r="G83" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.25">
@@ -2732,10 +2714,10 @@
         <v>23</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E84" s="5"/>
     </row>
@@ -2744,10 +2726,10 @@
         <v>56</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E85" s="5"/>
     </row>
